--- a/exports/trend_1d/LAURUSLABS_full_report.xlsx
+++ b/exports/trend_1d/LAURUSLABS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>11.47</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H2" t="n">
-        <v>110</v>
+        <v>105.45</v>
       </c>
       <c r="I2" t="n">
         <v>106.0743980021959</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K2" t="n">
-        <v>13.05</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>4.88</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>15.09</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42892</v>
+        <v>42893</v>
       </c>
       <c r="H3" t="n">
-        <v>120.45</v>
+        <v>122.3</v>
       </c>
       <c r="I3" t="n">
         <v>121.0745123469086</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-14.22</v>
+        <v>-15.98</v>
       </c>
       <c r="L3" t="n">
-        <v>17.26</v>
+        <v>17.54</v>
       </c>
       <c r="M3" t="n">
         <v>0.98</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>11.07</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42944</v>
+        <v>42947</v>
       </c>
       <c r="H4" t="n">
-        <v>118.4</v>
+        <v>116.15</v>
       </c>
       <c r="I4" t="n">
         <v>117.0756329214225</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.19</v>
+        <v>-5.03</v>
       </c>
       <c r="L4" t="n">
         <v>6.91</v>
       </c>
       <c r="M4" t="n">
-        <v>0.76</v>
+        <v>3.46</v>
       </c>
       <c r="N4" t="n">
         <v>2.23</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.23</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42978</v>
+        <v>42979</v>
       </c>
       <c r="H5" t="n">
-        <v>105.45</v>
+        <v>107.95</v>
       </c>
       <c r="I5" t="n">
         <v>107.6052663295547</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" t="n">
-        <v>9.210000000000001</v>
+        <v>7.06</v>
       </c>
       <c r="L5" t="n">
         <v>2.45</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>13.7</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43076</v>
+        <v>43077</v>
       </c>
       <c r="H6" t="n">
-        <v>103.6</v>
+        <v>100.65</v>
       </c>
       <c r="I6" t="n">
         <v>102.2580137417467</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.03</v>
+        <v>-6.76</v>
       </c>
       <c r="L6" t="n">
-        <v>6.95</v>
+        <v>7.55</v>
       </c>
       <c r="M6" t="n">
         <v>2.53</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>10.39</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43089</v>
+        <v>43090</v>
       </c>
       <c r="H7" t="n">
-        <v>107.25</v>
+        <v>112.7</v>
       </c>
       <c r="I7" t="n">
         <v>111.1028977247357</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.56</v>
+        <v>-11.97</v>
       </c>
       <c r="L7" t="n">
-        <v>7.4</v>
+        <v>13.76</v>
       </c>
       <c r="M7" t="n">
         <v>1.95</v>
       </c>
       <c r="N7" t="n">
-        <v>2.83</v>
+        <v>5.08</v>
       </c>
       <c r="O7" t="n">
         <v>-2.85</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>11.02</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43129</v>
+        <v>43130</v>
       </c>
       <c r="H8" t="n">
-        <v>107.85</v>
+        <v>103.45</v>
       </c>
       <c r="I8" t="n">
         <v>103.935822254959</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.3</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>5.9</v>
+        <v>9.85</v>
       </c>
       <c r="M8" t="n">
-        <v>1.17</v>
+        <v>4.31</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2</v>
+        <v>4.08</v>
       </c>
       <c r="O8" t="n">
         <v>5.08</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.42</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43171</v>
+        <v>43172</v>
       </c>
       <c r="H9" t="n">
-        <v>104.3</v>
+        <v>108.85</v>
       </c>
       <c r="I9" t="n">
         <v>108.7251822248231</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.82</v>
+        <v>-5.22</v>
       </c>
       <c r="L9" t="n">
         <v>6.33</v>
@@ -954,7 +1061,7 @@
         <v>2.49</v>
       </c>
       <c r="N9" t="n">
-        <v>3.33</v>
+        <v>4.36</v>
       </c>
       <c r="O9" t="n">
         <v>-4.08</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>10.59</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43230</v>
+        <v>43231</v>
       </c>
       <c r="H10" t="n">
-        <v>99.05</v>
+        <v>97.5</v>
       </c>
       <c r="I10" t="n">
         <v>98.28162996549466</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K10" t="n">
-        <v>-9</v>
+        <v>-10.43</v>
       </c>
       <c r="L10" t="n">
-        <v>11.21</v>
+        <v>12.17</v>
       </c>
       <c r="M10" t="n">
         <v>2.36</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>6.69</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43259</v>
+        <v>43262</v>
       </c>
       <c r="H11" t="n">
-        <v>96.7</v>
+        <v>100.05</v>
       </c>
       <c r="I11" t="n">
         <v>98.65244033740717</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K11" t="n">
-        <v>0.82</v>
+        <v>-2.62</v>
       </c>
       <c r="L11" t="n">
-        <v>0.92</v>
+        <v>3.79</v>
       </c>
       <c r="M11" t="n">
         <v>1.46</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>10.98</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43278</v>
+        <v>43279</v>
       </c>
       <c r="H12" t="n">
-        <v>91.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>91.14282980640432</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>-8.75</v>
+        <v>-9.65</v>
       </c>
       <c r="L12" t="n">
-        <v>9.449999999999999</v>
+        <v>10.34</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.06</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43419</v>
+        <v>43420</v>
       </c>
       <c r="H13" t="n">
-        <v>76.45</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>79.2918979147544</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K13" t="n">
-        <v>15.43</v>
+        <v>11.67</v>
       </c>
       <c r="L13" t="n">
         <v>11.28</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>13.13</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43493</v>
+        <v>43494</v>
       </c>
       <c r="H14" t="n">
-        <v>72.75</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>71.65901128162351</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.890000000000001</v>
+        <v>-10.96</v>
       </c>
       <c r="L14" t="n">
-        <v>9.83</v>
+        <v>12.27</v>
       </c>
       <c r="M14" t="n">
         <v>1.71</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.73</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H15" t="n">
-        <v>70.05</v>
+        <v>73.25</v>
       </c>
       <c r="I15" t="n">
         <v>71.51701067453422</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K15" t="n">
-        <v>1.48</v>
+        <v>-3.02</v>
       </c>
       <c r="L15" t="n">
         <v>5.49</v>
@@ -1296,7 +1475,7 @@
         <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>3.42</v>
+        <v>4.57</v>
       </c>
       <c r="O15" t="n">
         <v>-2.27</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.09</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43612</v>
+        <v>43613</v>
       </c>
       <c r="H16" t="n">
-        <v>74.45</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>73.47559197332038</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K16" t="n">
-        <v>1.64</v>
+        <v>-1.84</v>
       </c>
       <c r="L16" t="n">
         <v>3.89</v>
@@ -1353,7 +1544,7 @@
         <v>1.37</v>
       </c>
       <c r="N16" t="n">
-        <v>2.86</v>
+        <v>3.43</v>
       </c>
       <c r="O16" t="n">
         <v>4.57</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.57</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43647</v>
+        <v>43648</v>
       </c>
       <c r="H17" t="n">
-        <v>69.45</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>70.71723610189227</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K17" t="n">
-        <v>3.41</v>
+        <v>1.39</v>
       </c>
       <c r="L17" t="n">
         <v>4.17</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43679</v>
+        <v>43682</v>
       </c>
       <c r="H18" t="n">
-        <v>67.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="I18" t="n">
         <v>65.00216720589685</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.94</v>
+        <v>-9.73</v>
       </c>
       <c r="L18" t="n">
-        <v>7.76</v>
+        <v>10.79</v>
       </c>
       <c r="M18" t="n">
-        <v>2.58</v>
+        <v>5.79</v>
       </c>
       <c r="N18" t="n">
-        <v>3.98</v>
+        <v>5.04</v>
       </c>
       <c r="O18" t="n">
         <v>2.09</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>11.73</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43714</v>
+        <v>43717</v>
       </c>
       <c r="H19" t="n">
-        <v>68.2</v>
+        <v>70.2</v>
       </c>
       <c r="I19" t="n">
         <v>69.99648993378246</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.56</v>
+        <v>-9.69</v>
       </c>
       <c r="L19" t="n">
-        <v>8.75</v>
+        <v>10.94</v>
       </c>
       <c r="M19" t="n">
         <v>3.39</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>9.41</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43742</v>
+        <v>43745</v>
       </c>
       <c r="H20" t="n">
-        <v>71</v>
+        <v>66.5</v>
       </c>
       <c r="I20" t="n">
         <v>66.79561661854864</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K20" t="n">
-        <v>1.14</v>
+        <v>-5.27</v>
       </c>
       <c r="L20" t="n">
-        <v>4.56</v>
+        <v>7.12</v>
       </c>
       <c r="M20" t="n">
         <v>1.83</v>
       </c>
       <c r="N20" t="n">
-        <v>3.74</v>
+        <v>6.34</v>
       </c>
       <c r="O20" t="n">
         <v>2.93</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>15.59</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43765</v>
+        <v>43767</v>
       </c>
       <c r="H21" t="n">
-        <v>70.34999999999999</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>71.11050601405064</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.79</v>
+        <v>-6.99</v>
       </c>
       <c r="L21" t="n">
         <v>8.42</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>11.73</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43783</v>
+        <v>43784</v>
       </c>
       <c r="H22" t="n">
-        <v>71.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>68.99910245028664</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.87</v>
       </c>
       <c r="L22" t="n">
-        <v>1.34</v>
+        <v>5.13</v>
       </c>
       <c r="M22" t="n">
         <v>1.34</v>
       </c>
       <c r="N22" t="n">
-        <v>2.43</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
         <v>1.14</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>14.38</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43817</v>
+        <v>43818</v>
       </c>
       <c r="H23" t="n">
-        <v>71.2</v>
+        <v>74.3</v>
       </c>
       <c r="I23" t="n">
         <v>73.69758291879995</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.09</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>6.14</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>0.95</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.07</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H24" t="n">
-        <v>82.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>80.1938558506626</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K24" t="n">
-        <v>11.17</v>
+        <v>-1.62</v>
       </c>
       <c r="L24" t="n">
         <v>4.98</v>
@@ -1809,7 +2096,7 @@
         <v>2.79</v>
       </c>
       <c r="N24" t="n">
-        <v>4.18</v>
+        <v>11.5</v>
       </c>
       <c r="O24" t="n">
         <v>4.35</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>23.36</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43929</v>
+        <v>43930</v>
       </c>
       <c r="H25" t="n">
-        <v>78.40000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>81.39234385535748</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.25</v>
+        <v>-12.65</v>
       </c>
       <c r="L25" t="n">
         <v>16.14</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>23.64</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43959</v>
+        <v>43962</v>
       </c>
       <c r="H26" t="n">
-        <v>88.15000000000001</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>86.25468793572665</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K26" t="n">
-        <v>7.04</v>
+        <v>4.25</v>
       </c>
       <c r="L26" t="n">
         <v>5.16</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>24.36</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43994</v>
+        <v>43997</v>
       </c>
       <c r="H27" t="n">
-        <v>98.5</v>
+        <v>101.65</v>
       </c>
       <c r="I27" t="n">
         <v>101.2755831311952</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K27" t="n">
-        <v>-14.74</v>
+        <v>-18.4</v>
       </c>
       <c r="L27" t="n">
-        <v>15.61</v>
+        <v>19.92</v>
       </c>
       <c r="M27" t="n">
         <v>1.47</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.13</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44137</v>
+        <v>44138</v>
       </c>
       <c r="H28" t="n">
-        <v>300.85</v>
+        <v>291.35</v>
       </c>
       <c r="I28" t="n">
         <v>291.8442508742931</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K28" t="n">
-        <v>195.97</v>
+        <v>186.62</v>
       </c>
       <c r="L28" t="n">
         <v>4.57</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>20.99</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44162</v>
+        <v>44166</v>
       </c>
       <c r="H29" t="n">
-        <v>316.85</v>
+        <v>322.9</v>
       </c>
       <c r="I29" t="n">
         <v>319.8314884296254</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.75</v>
+        <v>-10.83</v>
       </c>
       <c r="L29" t="n">
-        <v>10.18</v>
+        <v>12.1</v>
       </c>
       <c r="M29" t="n">
         <v>3.35</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>15.87</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44404</v>
+        <v>44405</v>
       </c>
       <c r="H30" t="n">
-        <v>632.05</v>
+        <v>618.5</v>
       </c>
       <c r="I30" t="n">
         <v>623.6007784525914</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K30" t="n">
-        <v>95.73999999999999</v>
+        <v>91.55</v>
       </c>
       <c r="L30" t="n">
         <v>3.69</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>162</v>
+        <v>163</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>12.45</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44413</v>
+        <v>44414</v>
       </c>
       <c r="H31" t="n">
-        <v>671.55</v>
+        <v>679.8</v>
       </c>
       <c r="I31" t="n">
         <v>678.6048113989194</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K31" t="n">
-        <v>-8.58</v>
+        <v>-9.91</v>
       </c>
       <c r="L31" t="n">
-        <v>8.81</v>
+        <v>11.03</v>
       </c>
       <c r="M31" t="n">
         <v>1.17</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>10.24</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44428</v>
+        <v>44431</v>
       </c>
       <c r="H32" t="n">
-        <v>679.8</v>
+        <v>637.7</v>
       </c>
       <c r="I32" t="n">
         <v>645.3713223405035</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>-6.19</v>
       </c>
       <c r="L32" t="n">
-        <v>0.99</v>
+        <v>7.61</v>
       </c>
       <c r="M32" t="n">
         <v>0.5</v>
       </c>
       <c r="N32" t="n">
-        <v>2.53</v>
+        <v>6.19</v>
       </c>
       <c r="O32" t="n">
         <v>1.23</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>15.02</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44475</v>
+        <v>44476</v>
       </c>
       <c r="H33" t="n">
-        <v>626.9</v>
+        <v>650.65</v>
       </c>
       <c r="I33" t="n">
         <v>647.694837216316</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K33" t="n">
-        <v>1.69</v>
+        <v>-2.03</v>
       </c>
       <c r="L33" t="n">
         <v>7.32</v>
       </c>
       <c r="M33" t="n">
-        <v>0.73</v>
+        <v>2.73</v>
       </c>
       <c r="N33" t="n">
         <v>5.34</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44488</v>
+        <v>44489</v>
       </c>
       <c r="H34" t="n">
-        <v>617</v>
+        <v>599.45</v>
       </c>
       <c r="I34" t="n">
         <v>600.6116457359313</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.17</v>
+        <v>-7.87</v>
       </c>
       <c r="L34" t="n">
-        <v>6.55</v>
+        <v>9.26</v>
       </c>
       <c r="M34" t="n">
-        <v>0.02</v>
+        <v>0.32</v>
       </c>
       <c r="N34" t="n">
         <v>4.36</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.27</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44524</v>
+        <v>44525</v>
       </c>
       <c r="H35" t="n">
-        <v>502.1</v>
+        <v>535.05</v>
       </c>
       <c r="I35" t="n">
         <v>529.7060208243781</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K35" t="n">
-        <v>16.24</v>
+        <v>10.74</v>
       </c>
       <c r="L35" t="n">
         <v>2.92</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>16.78</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44580</v>
+        <v>44581</v>
       </c>
       <c r="H36" t="n">
-        <v>497.4</v>
+        <v>485.25</v>
       </c>
       <c r="I36" t="n">
         <v>488.1810516221669</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K36" t="n">
-        <v>-7.04</v>
+        <v>-9.31</v>
       </c>
       <c r="L36" t="n">
         <v>12.53</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>10.77</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44592</v>
+        <v>44593</v>
       </c>
       <c r="H37" t="n">
-        <v>502.7</v>
+        <v>524.45</v>
       </c>
       <c r="I37" t="n">
         <v>513.8573232399415</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.6</v>
+        <v>-8.08</v>
       </c>
       <c r="L37" t="n">
-        <v>6.5</v>
+        <v>8.65</v>
       </c>
       <c r="M37" t="n">
         <v>0.9</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>14.76</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H38" t="n">
-        <v>576.15</v>
+        <v>564.55</v>
       </c>
       <c r="I38" t="n">
         <v>565.6403512775331</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K38" t="n">
-        <v>9.859999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="L38" t="n">
         <v>5.42</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>11.17</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44754</v>
+        <v>44755</v>
       </c>
       <c r="H39" t="n">
-        <v>492.55</v>
+        <v>512.65</v>
       </c>
       <c r="I39" t="n">
         <v>507.5624089174576</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K39" t="n">
-        <v>12.75</v>
+        <v>9.19</v>
       </c>
       <c r="L39" t="n">
         <v>2.74</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.83</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44813</v>
+        <v>44816</v>
       </c>
       <c r="H40" t="n">
-        <v>555.45</v>
+        <v>546.7</v>
       </c>
       <c r="I40" t="n">
         <v>549.007321473516</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K40" t="n">
-        <v>8.35</v>
+        <v>6.64</v>
       </c>
       <c r="L40" t="n">
         <v>6.13</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45027</v>
+        <v>45028</v>
       </c>
       <c r="H41" t="n">
-        <v>302.05</v>
+        <v>323.1</v>
       </c>
       <c r="I41" t="n">
         <v>315.0592727988383</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K41" t="n">
-        <v>44.75</v>
+        <v>40.9</v>
       </c>
       <c r="L41" t="n">
         <v>2.19</v>
@@ -2778,7 +3269,7 @@
         <v>1.72</v>
       </c>
       <c r="N41" t="n">
-        <v>3.99</v>
+        <v>6.97</v>
       </c>
       <c r="O41" t="n">
         <v>-1.58</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>8</v>
+      </c>
+      <c r="U41" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.78</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45134</v>
+        <v>45135</v>
       </c>
       <c r="H42" t="n">
-        <v>343.9</v>
+        <v>337.8</v>
       </c>
       <c r="I42" t="n">
         <v>338.5986850903225</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K42" t="n">
-        <v>6.44</v>
+        <v>4.55</v>
       </c>
       <c r="L42" t="n">
         <v>13.7</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>10.22</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45140</v>
+        <v>45141</v>
       </c>
       <c r="H43" t="n">
-        <v>364.6</v>
+        <v>384.35</v>
       </c>
       <c r="I43" t="n">
         <v>372.3135761343109</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K43" t="n">
-        <v>-7.93</v>
+        <v>-13.78</v>
       </c>
       <c r="L43" t="n">
-        <v>8.94</v>
+        <v>14.15</v>
       </c>
       <c r="M43" t="n">
         <v>0.5</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>5.42</v>
       </c>
       <c r="O43" t="n">
         <v>-1.77</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>12.26</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H44" t="n">
-        <v>400.95</v>
+        <v>362.4</v>
       </c>
       <c r="I44" t="n">
         <v>379.9222927217575</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K44" t="n">
-        <v>4.32</v>
+        <v>-5.71</v>
       </c>
       <c r="L44" t="n">
-        <v>5.14</v>
+        <v>7.64</v>
       </c>
       <c r="M44" t="n">
-        <v>1.84</v>
+        <v>3.23</v>
       </c>
       <c r="N44" t="n">
-        <v>5.72</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="O44" t="n">
         <v>5.42</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>16.15</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45275</v>
+        <v>45278</v>
       </c>
       <c r="H45" t="n">
-        <v>385.7</v>
+        <v>399.35</v>
       </c>
       <c r="I45" t="n">
         <v>393.1624883388874</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.43</v>
+        <v>-10.2</v>
       </c>
       <c r="L45" t="n">
-        <v>10.83</v>
+        <v>10.91</v>
       </c>
       <c r="M45" t="n">
         <v>1.39</v>
       </c>
       <c r="N45" t="n">
-        <v>2.89</v>
+        <v>3.54</v>
       </c>
       <c r="O45" t="n">
         <v>-9.609999999999999</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H46" t="n">
-        <v>401.85</v>
+        <v>398.95</v>
       </c>
       <c r="I46" t="n">
         <v>399.1738936861934</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K46" t="n">
-        <v>0.63</v>
+        <v>-0.1</v>
       </c>
       <c r="L46" t="n">
         <v>4.85</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>9.81</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45353</v>
+        <v>45355</v>
       </c>
       <c r="H47" t="n">
-        <v>408.9</v>
+        <v>417.55</v>
       </c>
       <c r="I47" t="n">
         <v>415.6515692637973</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.49</v>
+        <v>-4.66</v>
       </c>
       <c r="L47" t="n">
-        <v>3.8</v>
+        <v>4.94</v>
       </c>
       <c r="M47" t="n">
         <v>0.87</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>7.75</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45369</v>
+        <v>45370</v>
       </c>
       <c r="H48" t="n">
-        <v>397.5</v>
+        <v>387.25</v>
       </c>
       <c r="I48" t="n">
         <v>392.8009756883997</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.8</v>
+        <v>-7.26</v>
       </c>
       <c r="L48" t="n">
-        <v>6.72</v>
+        <v>7.5</v>
       </c>
       <c r="M48" t="n">
         <v>0.38</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>10.84</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H49" t="n">
-        <v>415.25</v>
+        <v>439.85</v>
       </c>
       <c r="I49" t="n">
         <v>419.9049039712901</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K49" t="n">
-        <v>-7.23</v>
+        <v>-13.58</v>
       </c>
       <c r="L49" t="n">
-        <v>7.67</v>
+        <v>15.69</v>
       </c>
       <c r="M49" t="n">
         <v>1.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3.62</v>
+        <v>5.92</v>
       </c>
       <c r="O49" t="n">
         <v>-2.58</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>12.06</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45442</v>
+        <v>45443</v>
       </c>
       <c r="H50" t="n">
-        <v>427.85</v>
+        <v>418.95</v>
       </c>
       <c r="I50" t="n">
         <v>420.2164670776189</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.73</v>
+        <v>-4.75</v>
       </c>
       <c r="L50" t="n">
         <v>6.31</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>10.32</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45477</v>
+        <v>45478</v>
       </c>
       <c r="H51" t="n">
-        <v>454.45</v>
+        <v>477.15</v>
       </c>
       <c r="I51" t="n">
         <v>454.6302647574365</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K51" t="n">
-        <v>-8.470000000000001</v>
+        <v>-13.89</v>
       </c>
       <c r="L51" t="n">
-        <v>9.91</v>
+        <v>14.92</v>
       </c>
       <c r="M51" t="n">
         <v>1.47</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>10.38</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45495</v>
+        <v>45496</v>
       </c>
       <c r="H52" t="n">
-        <v>441.5</v>
+        <v>430.45</v>
       </c>
       <c r="I52" t="n">
         <v>433.8344663857996</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.47</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>8.609999999999999</v>
+        <v>11.88</v>
       </c>
       <c r="M52" t="n">
         <v>0.23</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>10.17</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45538</v>
+        <v>45539</v>
       </c>
       <c r="H53" t="n">
-        <v>470.1</v>
+        <v>475.6</v>
       </c>
       <c r="I53" t="n">
         <v>470.8321568492395</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K53" t="n">
-        <v>-9.210000000000001</v>
+        <v>-10.49</v>
       </c>
       <c r="L53" t="n">
-        <v>9.890000000000001</v>
+        <v>10.93</v>
       </c>
       <c r="M53" t="n">
         <v>1.18</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45554</v>
+        <v>45555</v>
       </c>
       <c r="H54" t="n">
-        <v>470.4</v>
+        <v>467.35</v>
       </c>
       <c r="I54" t="n">
         <v>467.4465377592641</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.09</v>
+        <v>-1.73</v>
       </c>
       <c r="L54" t="n">
         <v>3.07</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>10.18</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45579</v>
+        <v>45580</v>
       </c>
       <c r="H55" t="n">
-        <v>478.95</v>
+        <v>482</v>
       </c>
       <c r="I55" t="n">
         <v>479.3981608758536</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.48</v>
+        <v>-3.13</v>
       </c>
       <c r="L55" t="n">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="M55" t="n">
         <v>0.7</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>9.24</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H56" t="n">
-        <v>583.7</v>
+        <v>559.05</v>
       </c>
       <c r="I56" t="n">
         <v>565.8931378672768</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K56" t="n">
-        <v>21.1</v>
+        <v>15.99</v>
       </c>
       <c r="L56" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N56" t="n">
         <v>4.79</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>11.98</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45691</v>
+        <v>45692</v>
       </c>
       <c r="H57" t="n">
-        <v>586.35</v>
+        <v>611.95</v>
       </c>
       <c r="I57" t="n">
         <v>611.8657795571417</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.88</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>9.59</v>
+        <v>9.92</v>
       </c>
       <c r="M57" t="n">
         <v>4.07</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>16.8</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H58" t="n">
-        <v>601</v>
+        <v>546.2</v>
       </c>
       <c r="I58" t="n">
         <v>560.5504795775059</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.79</v>
+        <v>-10.74</v>
       </c>
       <c r="L58" t="n">
-        <v>4.4</v>
+        <v>13.14</v>
       </c>
       <c r="M58" t="n">
         <v>0.65</v>
       </c>
       <c r="N58" t="n">
-        <v>2.9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="O58" t="n">
         <v>4.37</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>20.95</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H59" t="n">
-        <v>587.15</v>
+        <v>606.1</v>
       </c>
       <c r="I59" t="n">
         <v>602.3203514758158</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.5</v>
+        <v>-10.97</v>
       </c>
       <c r="L59" t="n">
-        <v>10.58</v>
+        <v>11.5</v>
       </c>
       <c r="M59" t="n">
         <v>0.6899999999999999</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>12.69</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H60" t="n">
-        <v>574.45</v>
+        <v>561.25</v>
       </c>
       <c r="I60" t="n">
         <v>566.1016764069325</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K60" t="n">
-        <v>-5.22</v>
+        <v>-7.4</v>
       </c>
       <c r="L60" t="n">
-        <v>7.36</v>
+        <v>14.59</v>
       </c>
       <c r="M60" t="n">
-        <v>0.39</v>
+        <v>9.83</v>
       </c>
       <c r="N60" t="n">
         <v>7.44</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>10.98</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H61" t="n">
-        <v>605.85</v>
+        <v>625.15</v>
       </c>
       <c r="I61" t="n">
         <v>622.8988921103846</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.95</v>
+        <v>-11.39</v>
       </c>
       <c r="L61" t="n">
-        <v>8.33</v>
+        <v>11.56</v>
       </c>
       <c r="M61" t="n">
         <v>3.68</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>14.88</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H62" t="n">
-        <v>896.35</v>
+        <v>832.3</v>
       </c>
       <c r="I62" t="n">
         <v>866.7930344980622</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K62" t="n">
-        <v>43.38</v>
+        <v>33.14</v>
       </c>
       <c r="L62" t="n">
         <v>8.460000000000001</v>
@@ -3975,7 +4718,7 @@
         <v>2.4</v>
       </c>
       <c r="N62" t="n">
-        <v>3.92</v>
+        <v>7.15</v>
       </c>
       <c r="O62" t="n">
         <v>3.19</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>6</v>
+      </c>
+      <c r="U62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>12.8</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="H63" t="n">
-        <v>900.05</v>
+        <v>920.65</v>
       </c>
       <c r="I63" t="n">
         <v>915.6557362629837</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.140000000000001</v>
+        <v>-10.62</v>
       </c>
       <c r="L63" t="n">
-        <v>8.369999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="M63" t="n">
         <v>0.91</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="H64" t="n">
-        <v>1083</v>
+        <v>1043.2</v>
       </c>
       <c r="I64" t="n">
         <v>1061.451179359029</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K64" t="n">
-        <v>17.63</v>
+        <v>13.31</v>
       </c>
       <c r="L64" t="n">
         <v>2.09</v>
@@ -4089,7 +4856,7 @@
         <v>0.54</v>
       </c>
       <c r="N64" t="n">
-        <v>2.45</v>
+        <v>3.67</v>
       </c>
       <c r="O64" t="n">
         <v>2.29</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>9.27</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="H65" t="n">
-        <v>1028.5</v>
+        <v>1076.35</v>
       </c>
       <c r="I65" t="n">
         <v>1053.064625215935</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K65" t="n">
-        <v>1.41</v>
+        <v>-3.18</v>
       </c>
       <c r="L65" t="n">
         <v>5.34</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>11.03</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="H66" t="n">
-        <v>1003.4</v>
+        <v>960.8</v>
       </c>
       <c r="I66" t="n">
         <v>990.9753115476792</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K66" t="n">
-        <v>-6.78</v>
+        <v>-10.74</v>
       </c>
       <c r="L66" t="n">
-        <v>9.42</v>
+        <v>11.57</v>
       </c>
       <c r="M66" t="n">
         <v>4.26</v>
       </c>
       <c r="N66" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="O66" t="n">
         <v>4.65</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>15.24</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H67" t="n">
-        <v>1057.45</v>
+        <v>1082.45</v>
       </c>
       <c r="I67" t="n">
         <v>1073.211702787137</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K67" t="n">
-        <v>-10.06</v>
+        <v>-12.66</v>
       </c>
       <c r="L67" t="n">
-        <v>11.51</v>
+        <v>13.68</v>
       </c>
       <c r="M67" t="n">
         <v>2.76</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4320,6 +5135,14 @@
       <c r="Q68" t="n">
         <v>139</v>
       </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8496,7 +9319,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.6</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="6">
@@ -8506,7 +9329,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -8516,7 +9339,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8">
@@ -8526,7 +9349,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -8536,7 +9359,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="10">
@@ -8546,7 +9369,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="11">
@@ -8556,7 +9379,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -8566,7 +9389,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -8576,7 +9399,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40.9</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="14">
@@ -8586,7 +9409,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.48</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="15">
@@ -8596,7 +9419,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.67</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="16">
@@ -8606,7 +9429,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.71</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="17">
@@ -8616,7 +9439,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>195.97</v>
+        <v>186.62</v>
       </c>
     </row>
     <row r="18">
@@ -8626,7 +9449,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>37.9</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="19">
@@ -8636,7 +9459,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.13</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="20">
@@ -8646,7 +9469,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.82</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -8656,7 +9479,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.26</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="22">
@@ -8666,7 +9489,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -8676,7 +9499,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -8686,7 +9509,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="25">
@@ -8696,7 +9519,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.57</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="26">
@@ -8706,7 +9529,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.51</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="27">
@@ -8726,7 +9549,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
